--- a/data/paragraph_hate_speech_labeled.xlsx
+++ b/data/paragraph_hate_speech_labeled.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mdodovic\Desktop\LLM-HS-Detector\HateSpeech-LLM-Detector\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE69EFE7-3345-4410-8FEE-D290BF0E2C92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5A76511-B7A5-40BC-B299-9C6B852C0A1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2640" yWindow="2640" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Labels" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>ID</t>
   </si>
@@ -53,16 +53,73 @@
   <si>
     <t>6b,0,6b,1b,6b,0,0,0,0,0,0</t>
   </si>
+  <si>
+    <t>Rekoše mi da je „novinarka“ Tanjuga pitala ambasadora EU u Srbiji kako komentariše pozivanje reportera televizije N1, to jest mene, da se narod naoruža strpljenjem. Juče sam u reporterskom javljanju, u razgovoru sa koleginicom Majom Dragić, namerno upotrebio tu frazu, dajući joj ironični smisao, a koju često koriste kolege kada upozoravaju na saobraćajne gužve u gradu. Neverovatno, jesu li ti ljudi koji ovo tumače pozivanjem na naoružavanje naroda glupi ili pokvareni, ili su jedno i drugo? Mladoj „koleginici“ bih poručio da se naoruža znanjem, vaspitanjem i poštovanjem. Biće novinarstva i posle ove gamadi na vlasti, nadam se nikada više i ovakve propagande, koja je samo u jednoj funkciji – zatupljivanja građana Srbije. Današnji srpski novinari ne smeju biti tako plitkoumni i retardirani.</t>
+  </si>
+  <si>
+    <t>Не постоје две Србије, не постоје два српска народа, не постоје две отаџбине. Не смемо да дозволимо непријатељима да нас поделе и посвађају. Ми нисмо дивљи као Шиптари, нити великоусташе као Хрвати. Нашим потомцима морамо да оставимо јаку, стабилну и просперитетну Србију која ће бити довољно снажна да победи сваког непријатеља и да буде вечна. Другосрбијанци неће моћи да дођу на власт без избора, као што они мисле.</t>
+  </si>
+  <si>
+    <t>Ovu odvratnu Dijanu Hrku bih pitala kako nije okacila ni jednu sliku sina na svojim drustvenim mrezama sve dok nije poginuo??? Ponaša se kao neka prosjakinja i ciganka, i smatra da sada svi treba da je sažaljevamo. A znamo da nije bila u dobrim odnosima sa sinom. I ovi drugosrbijanci što je podržavaju su sramota ljudskog roda.</t>
+  </si>
+  <si>
+    <t>Postupci budale uvek nadmašuju očekivanja pametnog čoveka. Možda je ova žena od bola izgubila razum. Ali šta je sa ostalima?
+Ovo definitivno nije Srbija za koju se vredi boriti. Razlika između ovoga i Vučićevog ološa jeste isključivo - terminološka! Da li su Srbi toliko zatucan narod postali? Nekada stvarno ne mogu da verujem sa kakvim imbecilima mi delimo isti prostor i vazduh.</t>
+  </si>
+  <si>
+    <t>Gde su sada košarkaši i saigrači da brane Vladimira Štimca? A sećamo se da je taj lik uvek kao majmun visio iza klupe reprezentacije i vrteo peškirom da digne atmosferu kada smo pobeđivali i kada nam se košarka nije raspala. A pamtimo i onaj spor... to je bilo pre 10 godina. a nisu ga blokirali cigani, posebno ne narkodileri zvani Delije, nego Čović. Medjutim sad su se nagodili i Čović je prepustio kk, a delije su kriminogene kurvetine na prodaju i pederi i ne podržavaju ovog lika. Mafijaški klan braće Vučić kada je ušao među ciganski klub, odmah im je krenulo na bolje. A oni su zapravo ništa drugo nego FMP franšiza. Sada će Čovke da nastavi na uništava srpsku košarku i na reprezentativnom nivou. Videli smo šta je uradio sa sjajnom Pešićevom reprezentacijom ćoravi kreten, treba ga streljati za primer.</t>
+  </si>
+  <si>
+    <t>Alo Delije, Cigani kako se već zovete godinama ste čutali a sinoć progovorili, ALI ali?? Ovaj vaš postupak mi Grobari, koji godinama trpimo teror i skandiramo VČĆU PEDERU, shvatamo kao iskrcavanje sa TITANIKA.. PAMTIĆEMO VAŠE ĆUTANJE I PODRŽAVANJE kriminalne mafijaške hobotnice NAPREDNJAKA i Aleksandra Vučića. Vi Cigani ste govna velika i treba vas uništiti svuda u svetu! Jednako ste jadni i bedni kao i sve pristalice Srpske napredne stranke i Vučićeve perjanice iz Zvezde. Kad se zabrani sns mora da se zabrani i arkanova ćerka firma Gejlije sever. Vratite cigane oni imaju više časti. Cigani su braća, delije su neprijatelj.</t>
+  </si>
+  <si>
+    <t>Kao treća generacija navijača Zvezde, tvrdim, kada su Cigani postali Delije sve je ošloukurac...mene sramota a Grobarima svaka čast. Delije podignite glavu mi stariji cigani nemamo mladost koju vi imate, dozvoli ste da na nasoj marakani red zavode crnokosuljasi mi nismo to dozvolili ni za vreme tita. Zapad smo stitili sa ekipama koje su sedele uz severnu ogradu. ..šta reći za naše srbe koji se ponose nadimkom "cigani" i "delije (turski konjanici)"... Ne može mešavina smrdljivih Cigana i turskih konjušara da izađe na dobro.</t>
+  </si>
+  <si>
+    <t>Ova dešavanja su pokrenula lavinu kod zabrinutih roditelja koji su tražili hitan sastanak sa članovima prinudne uprave kluba kako bi dobili odgovore o stanju kluba i izrazili zabrinutost za budućnost svoje dece. Umesto smirivanja strasti i pronalaženja rešenja, odgovor zakonskog zastupnika Marka Marjanovića na negodovanje roditelja o trenutnim dešavanjima je bio kratak: "Ako vi mislite da su Nikola Stojić i Nikola Simović najbolji treneri za vašu decu, slobodno možete da tražite ispisnice". Posle ovakve izjave ceo juniorski pogon je napustio ovaj klub. Ovakve izjave svakako nisu dostojne funkcije na koju je Marjanović postavljen od strane čelnika JSD Partizan. Od kako je postavljena privremena uprava pre dva meseca, ona je uspela da razmontira veslački klub u paramparčad. Posle deljenja otkaza i pretnjama zaposlenima, stiglu su na red veslači i veslačice - neprocenjivo bogatstvo koje klub poseduje. Višedecenijski rad i istorija jednog kluba je nestala za samo dva meseca zahavljujući naprednjačkim smradovima i Ćacijima. Treba ih sve za jaja okačiti na Terazijama. Uništavaju srpsku omladinu kao da su Hrvati Ustaše. Videće sada deca da mafijaši, keramičari, kondukteri, frizeri, grobari i oni bez osnovne škole postadoše državni funkcioneri pa će mnogi i od njih da probaju.</t>
+  </si>
+  <si>
+    <t>0,0,6b,0,6b,6b</t>
+  </si>
+  <si>
+    <t>0,0,1c,0,1c</t>
+  </si>
+  <si>
+    <t>4a,6a,0,1c</t>
+  </si>
+  <si>
+    <t>0,0,0,0,6b,1b,4b</t>
+  </si>
+  <si>
+    <t>0,0,0,0,0,0,6b,0,1b,7</t>
+  </si>
+  <si>
+    <t>7,0,7,1b</t>
+  </si>
+  <si>
+    <t>7,7,6b,7,6b,6b,7,7</t>
+  </si>
+  <si>
+    <t>0,7,0,0,7,7,7,0,7,6b</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -118,18 +175,27 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -350,1182 +416,1239 @@
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.7109375" customWidth="1"/>
-    <col min="2" max="2" width="96.85546875" customWidth="1"/>
-    <col min="3" max="8" width="8.7109375" customWidth="1"/>
+    <col min="2" max="2" width="96.42578125" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="8" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2">
+    <row r="2" spans="1:3" s="6" customFormat="1" ht="135" x14ac:dyDescent="0.25">
+      <c r="A2" s="6">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="6" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="3"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-    </row>
-    <row r="6" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="3"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-    </row>
-    <row r="7" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="3"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-    </row>
-    <row r="8" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="3"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-    </row>
-    <row r="9" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="3"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-    </row>
-    <row r="10" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="3"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-    </row>
-    <row r="11" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" s="6" customFormat="1" ht="120" x14ac:dyDescent="0.25">
+      <c r="A3" s="6">
+        <v>2</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+      <c r="A4" s="6">
+        <v>3</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A5" s="6">
+        <v>4</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+      <c r="A6" s="6">
+        <v>5</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" s="6" customFormat="1" ht="120" x14ac:dyDescent="0.25">
+      <c r="A7" s="6">
+        <v>6</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" s="6" customFormat="1" ht="105" x14ac:dyDescent="0.25">
+      <c r="A8" s="6">
+        <v>7</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" s="6" customFormat="1" ht="90" x14ac:dyDescent="0.25">
+      <c r="A9" s="6">
+        <v>8</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" s="6" customFormat="1" ht="195" x14ac:dyDescent="0.25">
+      <c r="A10" s="6">
+        <v>9</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="3"/>
-      <c r="B11" s="2"/>
+      <c r="B11" s="7"/>
       <c r="C11" s="2"/>
     </row>
-    <row r="12" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="3"/>
-      <c r="B12" s="2"/>
+      <c r="B12" s="7"/>
       <c r="C12" s="2"/>
     </row>
-    <row r="13" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="3"/>
-      <c r="B13" s="2"/>
+      <c r="B13" s="7"/>
       <c r="C13" s="2"/>
     </row>
-    <row r="14" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="3"/>
-      <c r="B14" s="2"/>
+      <c r="B14" s="7"/>
       <c r="C14" s="2"/>
     </row>
-    <row r="15" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="3"/>
-      <c r="B15" s="2"/>
+      <c r="B15" s="7"/>
       <c r="C15" s="2"/>
     </row>
-    <row r="16" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="3"/>
-      <c r="B16" s="2"/>
+      <c r="B16" s="7"/>
       <c r="C16" s="2"/>
     </row>
-    <row r="17" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="3"/>
-      <c r="B17" s="2"/>
+      <c r="B17" s="7"/>
       <c r="C17" s="2"/>
     </row>
-    <row r="18" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="3"/>
-      <c r="B18" s="2"/>
+      <c r="B18" s="7"/>
       <c r="C18" s="2"/>
     </row>
-    <row r="19" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="3"/>
-      <c r="B19" s="2"/>
+      <c r="B19" s="7"/>
       <c r="C19" s="2"/>
     </row>
-    <row r="20" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="3"/>
-      <c r="B20" s="2"/>
+      <c r="B20" s="7"/>
       <c r="C20" s="2"/>
     </row>
-    <row r="21" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="3"/>
-      <c r="B21" s="2"/>
+      <c r="B21" s="7"/>
       <c r="C21" s="2"/>
     </row>
-    <row r="22" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="3"/>
-      <c r="B22" s="2"/>
+      <c r="B22" s="7"/>
       <c r="C22" s="2"/>
     </row>
-    <row r="23" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="3"/>
-      <c r="B23" s="2"/>
+      <c r="B23" s="7"/>
       <c r="C23" s="2"/>
     </row>
-    <row r="24" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="3"/>
-      <c r="B24" s="2"/>
+      <c r="B24" s="7"/>
       <c r="C24" s="2"/>
     </row>
-    <row r="25" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="3"/>
-      <c r="B25" s="2"/>
+      <c r="B25" s="7"/>
       <c r="C25" s="2"/>
     </row>
-    <row r="26" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="3"/>
-      <c r="B26" s="2"/>
+      <c r="B26" s="7"/>
       <c r="C26" s="2"/>
     </row>
-    <row r="27" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="3"/>
-      <c r="B27" s="2"/>
+      <c r="B27" s="7"/>
       <c r="C27" s="2"/>
     </row>
     <row r="28" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3"/>
-      <c r="B28" s="2"/>
+      <c r="B28" s="7"/>
       <c r="C28" s="2"/>
     </row>
     <row r="29" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3"/>
-      <c r="B29" s="2"/>
+      <c r="B29" s="7"/>
       <c r="C29" s="2"/>
     </row>
     <row r="30" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3"/>
-      <c r="B30" s="2"/>
+      <c r="B30" s="7"/>
       <c r="C30" s="2"/>
     </row>
     <row r="31" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="3"/>
-      <c r="B31" s="2"/>
+      <c r="B31" s="7"/>
       <c r="C31" s="2"/>
     </row>
     <row r="32" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3"/>
-      <c r="B32" s="2"/>
+      <c r="B32" s="7"/>
       <c r="C32" s="2"/>
     </row>
     <row r="33" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="3"/>
-      <c r="B33" s="2"/>
+      <c r="B33" s="7"/>
       <c r="C33" s="2"/>
     </row>
     <row r="34" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3"/>
-      <c r="B34" s="2"/>
+      <c r="B34" s="7"/>
       <c r="C34" s="2"/>
     </row>
     <row r="35" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="3"/>
-      <c r="B35" s="2"/>
+      <c r="B35" s="7"/>
       <c r="C35" s="2"/>
     </row>
     <row r="36" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3"/>
-      <c r="B36" s="2"/>
+      <c r="B36" s="7"/>
       <c r="C36" s="2"/>
     </row>
     <row r="37" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="3"/>
-      <c r="B37" s="2"/>
+      <c r="B37" s="7"/>
       <c r="C37" s="2"/>
     </row>
     <row r="38" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3"/>
-      <c r="B38" s="2"/>
+      <c r="B38" s="7"/>
       <c r="C38" s="2"/>
     </row>
     <row r="39" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="3"/>
-      <c r="B39" s="2"/>
+      <c r="B39" s="7"/>
       <c r="C39" s="2"/>
     </row>
     <row r="40" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="3"/>
-      <c r="B40" s="2"/>
+      <c r="B40" s="7"/>
       <c r="C40" s="4"/>
     </row>
     <row r="41" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="3"/>
-      <c r="B41" s="2"/>
+      <c r="B41" s="7"/>
       <c r="C41" s="2"/>
     </row>
     <row r="42" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="3"/>
-      <c r="B42" s="2"/>
+      <c r="B42" s="7"/>
       <c r="C42" s="2"/>
     </row>
     <row r="43" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="3"/>
-      <c r="B43" s="2"/>
+      <c r="B43" s="7"/>
       <c r="C43" s="2"/>
     </row>
     <row r="44" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="3"/>
-      <c r="B44" s="2"/>
+      <c r="B44" s="7"/>
       <c r="C44" s="2"/>
     </row>
     <row r="45" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="3"/>
-      <c r="B45" s="2"/>
+      <c r="B45" s="7"/>
       <c r="C45" s="2"/>
     </row>
     <row r="46" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="3"/>
-      <c r="B46" s="2"/>
+      <c r="B46" s="7"/>
       <c r="C46" s="2"/>
     </row>
     <row r="47" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="3"/>
-      <c r="B47" s="2"/>
+      <c r="B47" s="7"/>
       <c r="C47" s="2"/>
     </row>
     <row r="48" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="3"/>
-      <c r="B48" s="2"/>
+      <c r="B48" s="7"/>
       <c r="C48" s="2"/>
     </row>
     <row r="49" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="3"/>
-      <c r="B49" s="2"/>
+      <c r="B49" s="7"/>
       <c r="C49" s="2"/>
     </row>
     <row r="50" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="3"/>
-      <c r="B50" s="2"/>
+      <c r="B50" s="7"/>
       <c r="C50" s="2"/>
     </row>
     <row r="51" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="3"/>
-      <c r="B51" s="2"/>
+      <c r="B51" s="7"/>
       <c r="C51" s="2"/>
     </row>
     <row r="52" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="3"/>
-      <c r="B52" s="2"/>
+      <c r="B52" s="7"/>
       <c r="C52" s="2"/>
     </row>
     <row r="53" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="3"/>
-      <c r="B53" s="2"/>
+      <c r="B53" s="7"/>
       <c r="C53" s="2"/>
     </row>
     <row r="54" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="3"/>
-      <c r="B54" s="2"/>
+      <c r="B54" s="7"/>
       <c r="C54" s="2"/>
     </row>
     <row r="55" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="3"/>
-      <c r="B55" s="2"/>
+      <c r="B55" s="7"/>
       <c r="C55" s="2"/>
     </row>
     <row r="56" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="3"/>
-      <c r="B56" s="2"/>
+      <c r="B56" s="7"/>
       <c r="C56" s="2"/>
     </row>
     <row r="57" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="3"/>
-      <c r="B57" s="2"/>
+      <c r="B57" s="7"/>
       <c r="C57" s="2"/>
     </row>
     <row r="58" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="3"/>
-      <c r="B58" s="2"/>
+      <c r="B58" s="7"/>
       <c r="C58" s="2"/>
     </row>
     <row r="59" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="3"/>
-      <c r="B59" s="2"/>
+      <c r="B59" s="7"/>
       <c r="C59" s="2"/>
     </row>
     <row r="60" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="3"/>
-      <c r="B60" s="2"/>
+      <c r="B60" s="7"/>
       <c r="C60" s="2"/>
     </row>
     <row r="61" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="3"/>
-      <c r="B61" s="2"/>
+      <c r="B61" s="7"/>
       <c r="C61" s="2"/>
     </row>
     <row r="62" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="3"/>
-      <c r="B62" s="2"/>
+      <c r="B62" s="7"/>
       <c r="C62" s="2"/>
     </row>
     <row r="63" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="3"/>
-      <c r="B63" s="2"/>
+      <c r="B63" s="7"/>
       <c r="C63" s="2"/>
     </row>
     <row r="64" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="3"/>
-      <c r="B64" s="2"/>
+      <c r="B64" s="7"/>
       <c r="C64" s="2"/>
     </row>
     <row r="65" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="3"/>
-      <c r="B65" s="2"/>
+      <c r="B65" s="7"/>
       <c r="C65" s="2"/>
     </row>
     <row r="66" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="3"/>
-      <c r="B66" s="2"/>
+      <c r="B66" s="7"/>
       <c r="C66" s="2"/>
     </row>
     <row r="67" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="3"/>
-      <c r="B67" s="2"/>
+      <c r="B67" s="7"/>
       <c r="C67" s="2"/>
     </row>
     <row r="68" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="3"/>
-      <c r="B68" s="2"/>
+      <c r="B68" s="7"/>
       <c r="C68" s="2"/>
     </row>
     <row r="69" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="3"/>
-      <c r="B69" s="2"/>
+      <c r="B69" s="7"/>
       <c r="C69" s="2"/>
     </row>
     <row r="70" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="3"/>
-      <c r="B70" s="2"/>
+      <c r="B70" s="7"/>
       <c r="C70" s="2"/>
     </row>
     <row r="71" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="3"/>
-      <c r="B71" s="2"/>
+      <c r="B71" s="7"/>
       <c r="C71" s="2"/>
     </row>
     <row r="72" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="3"/>
-      <c r="B72" s="2"/>
+      <c r="B72" s="7"/>
       <c r="C72" s="2"/>
     </row>
     <row r="73" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="3"/>
-      <c r="B73" s="2"/>
+      <c r="B73" s="7"/>
       <c r="C73" s="2"/>
     </row>
     <row r="74" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="3"/>
-      <c r="B74" s="2"/>
+      <c r="B74" s="7"/>
       <c r="C74" s="2"/>
     </row>
     <row r="75" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="3"/>
-      <c r="B75" s="2"/>
+      <c r="B75" s="7"/>
       <c r="C75" s="2"/>
     </row>
     <row r="76" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="3"/>
-      <c r="B76" s="2"/>
+      <c r="B76" s="7"/>
       <c r="C76" s="2"/>
     </row>
     <row r="77" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="3"/>
-      <c r="B77" s="2"/>
+      <c r="B77" s="7"/>
       <c r="C77" s="2"/>
     </row>
     <row r="78" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="3"/>
-      <c r="B78" s="2"/>
+      <c r="B78" s="7"/>
       <c r="C78" s="2"/>
     </row>
     <row r="79" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="3"/>
-      <c r="B79" s="2"/>
+      <c r="B79" s="7"/>
       <c r="C79" s="2"/>
     </row>
     <row r="80" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="3"/>
-      <c r="B80" s="2"/>
+      <c r="B80" s="7"/>
       <c r="C80" s="2"/>
     </row>
     <row r="81" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="3"/>
-      <c r="B81" s="2"/>
+      <c r="B81" s="7"/>
       <c r="C81" s="2"/>
     </row>
     <row r="82" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="3"/>
-      <c r="B82" s="2"/>
+      <c r="B82" s="7"/>
       <c r="C82" s="2"/>
     </row>
     <row r="83" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="3"/>
-      <c r="B83" s="2"/>
+      <c r="B83" s="7"/>
       <c r="C83" s="2"/>
     </row>
     <row r="84" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="3"/>
-      <c r="B84" s="2"/>
+      <c r="B84" s="7"/>
       <c r="C84" s="2"/>
     </row>
     <row r="85" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="3"/>
-      <c r="B85" s="2"/>
+      <c r="B85" s="7"/>
       <c r="C85" s="2"/>
     </row>
     <row r="86" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="3"/>
-      <c r="B86" s="2"/>
+      <c r="B86" s="7"/>
       <c r="C86" s="2"/>
     </row>
     <row r="87" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="3"/>
-      <c r="B87" s="2"/>
+      <c r="B87" s="7"/>
       <c r="C87" s="2"/>
     </row>
     <row r="88" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="3"/>
-      <c r="B88" s="2"/>
+      <c r="B88" s="7"/>
       <c r="C88" s="2"/>
     </row>
     <row r="89" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="3"/>
-      <c r="B89" s="2"/>
+      <c r="B89" s="7"/>
       <c r="C89" s="2"/>
     </row>
     <row r="90" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="3"/>
-      <c r="B90" s="2"/>
+      <c r="B90" s="7"/>
       <c r="C90" s="2"/>
     </row>
     <row r="91" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="3"/>
-      <c r="B91" s="2"/>
+      <c r="B91" s="7"/>
       <c r="C91" s="2"/>
     </row>
     <row r="92" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="3"/>
-      <c r="B92" s="2"/>
+      <c r="B92" s="7"/>
       <c r="C92" s="2"/>
     </row>
     <row r="93" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="3"/>
-      <c r="B93" s="2"/>
+      <c r="B93" s="7"/>
       <c r="C93" s="2"/>
     </row>
     <row r="94" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="3"/>
-      <c r="B94" s="2"/>
+      <c r="B94" s="7"/>
       <c r="C94" s="2"/>
     </row>
     <row r="95" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="3"/>
-      <c r="B95" s="2"/>
+      <c r="B95" s="7"/>
       <c r="C95" s="2"/>
     </row>
     <row r="96" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="3"/>
-      <c r="B96" s="2"/>
+      <c r="B96" s="7"/>
       <c r="C96" s="2"/>
     </row>
     <row r="97" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="3"/>
-      <c r="B97" s="2"/>
+      <c r="B97" s="7"/>
       <c r="C97" s="2"/>
     </row>
     <row r="98" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="3"/>
-      <c r="B98" s="2"/>
+      <c r="B98" s="7"/>
       <c r="C98" s="2"/>
     </row>
     <row r="99" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="3"/>
-      <c r="B99" s="2"/>
+      <c r="B99" s="7"/>
       <c r="C99" s="2"/>
     </row>
     <row r="100" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="3"/>
-      <c r="B100" s="2"/>
+      <c r="B100" s="7"/>
       <c r="C100" s="2"/>
     </row>
     <row r="101" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="3"/>
-      <c r="B101" s="2"/>
+      <c r="B101" s="7"/>
       <c r="C101" s="2"/>
     </row>
     <row r="102" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="3"/>
-      <c r="B102" s="2"/>
+      <c r="B102" s="7"/>
       <c r="C102" s="2"/>
     </row>
     <row r="103" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="3"/>
-      <c r="B103" s="2"/>
+      <c r="B103" s="7"/>
       <c r="C103" s="2"/>
     </row>
     <row r="104" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="3"/>
-      <c r="B104" s="2"/>
+      <c r="B104" s="7"/>
       <c r="C104" s="2"/>
     </row>
     <row r="105" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="3"/>
-      <c r="B105" s="2"/>
+      <c r="B105" s="7"/>
       <c r="C105" s="2"/>
     </row>
     <row r="106" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="3"/>
-      <c r="B106" s="2"/>
+      <c r="B106" s="7"/>
       <c r="C106" s="2"/>
     </row>
     <row r="107" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="3"/>
-      <c r="B107" s="2"/>
+      <c r="B107" s="7"/>
       <c r="C107" s="2"/>
     </row>
     <row r="108" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="3"/>
-      <c r="B108" s="2"/>
+      <c r="B108" s="7"/>
       <c r="C108" s="2"/>
     </row>
     <row r="109" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="3"/>
-      <c r="B109" s="2"/>
+      <c r="B109" s="7"/>
       <c r="C109" s="2"/>
     </row>
     <row r="110" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="3"/>
-      <c r="B110" s="2"/>
+      <c r="B110" s="7"/>
       <c r="C110" s="2"/>
     </row>
     <row r="111" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="3"/>
-      <c r="B111" s="2"/>
+      <c r="B111" s="7"/>
       <c r="C111" s="2"/>
     </row>
     <row r="112" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="3"/>
-      <c r="B112" s="2"/>
+      <c r="B112" s="7"/>
       <c r="C112" s="2"/>
     </row>
     <row r="113" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="3"/>
-      <c r="B113" s="2"/>
+      <c r="B113" s="7"/>
       <c r="C113" s="2"/>
     </row>
     <row r="114" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="3"/>
-      <c r="B114" s="2"/>
+      <c r="B114" s="7"/>
       <c r="C114" s="2"/>
     </row>
     <row r="115" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="3"/>
-      <c r="B115" s="2"/>
+      <c r="B115" s="7"/>
       <c r="C115" s="2"/>
     </row>
     <row r="116" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="3"/>
-      <c r="B116" s="2"/>
+      <c r="B116" s="7"/>
       <c r="C116" s="2"/>
     </row>
     <row r="117" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="3"/>
-      <c r="B117" s="2"/>
+      <c r="B117" s="7"/>
       <c r="C117" s="2"/>
     </row>
     <row r="118" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="3"/>
-      <c r="B118" s="2"/>
+      <c r="B118" s="7"/>
       <c r="C118" s="2"/>
     </row>
     <row r="119" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="3"/>
-      <c r="B119" s="2"/>
+      <c r="B119" s="7"/>
       <c r="C119" s="2"/>
     </row>
     <row r="120" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="3"/>
-      <c r="B120" s="2"/>
+      <c r="B120" s="7"/>
       <c r="C120" s="2"/>
     </row>
     <row r="121" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="3"/>
-      <c r="B121" s="2"/>
+      <c r="B121" s="7"/>
       <c r="C121" s="2"/>
     </row>
     <row r="122" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="3"/>
-      <c r="B122" s="2"/>
+      <c r="B122" s="7"/>
       <c r="C122" s="2"/>
     </row>
     <row r="123" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="3"/>
-      <c r="B123" s="2"/>
+      <c r="B123" s="7"/>
       <c r="C123" s="2"/>
     </row>
     <row r="124" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="3"/>
-      <c r="B124" s="2"/>
+      <c r="B124" s="7"/>
       <c r="C124" s="2"/>
     </row>
     <row r="125" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="3"/>
-      <c r="B125" s="2"/>
+      <c r="B125" s="7"/>
       <c r="C125" s="2"/>
     </row>
     <row r="126" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="3"/>
-      <c r="B126" s="2"/>
+      <c r="B126" s="7"/>
       <c r="C126" s="2"/>
     </row>
     <row r="127" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="3"/>
-      <c r="B127" s="2"/>
+      <c r="B127" s="7"/>
       <c r="C127" s="2"/>
     </row>
     <row r="128" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="3"/>
-      <c r="B128" s="2"/>
+      <c r="B128" s="7"/>
       <c r="C128" s="2"/>
     </row>
     <row r="129" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="3"/>
-      <c r="B129" s="2"/>
+      <c r="B129" s="7"/>
       <c r="C129" s="2"/>
     </row>
     <row r="130" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="3"/>
-      <c r="B130" s="2"/>
+      <c r="B130" s="7"/>
       <c r="C130" s="2"/>
     </row>
     <row r="131" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="3"/>
-      <c r="B131" s="2"/>
+      <c r="B131" s="7"/>
       <c r="C131" s="2"/>
     </row>
     <row r="132" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="3"/>
-      <c r="B132" s="2"/>
+      <c r="B132" s="7"/>
       <c r="C132" s="2"/>
     </row>
     <row r="133" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="3"/>
-      <c r="B133" s="2"/>
+      <c r="B133" s="7"/>
       <c r="C133" s="2"/>
     </row>
     <row r="134" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="3"/>
-      <c r="B134" s="2"/>
+      <c r="B134" s="7"/>
       <c r="C134" s="2"/>
     </row>
     <row r="135" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="3"/>
-      <c r="B135" s="2"/>
+      <c r="B135" s="7"/>
       <c r="C135" s="2"/>
     </row>
     <row r="136" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="3"/>
-      <c r="B136" s="2"/>
+      <c r="B136" s="7"/>
       <c r="C136" s="2"/>
     </row>
     <row r="137" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="3"/>
-      <c r="B137" s="2"/>
+      <c r="B137" s="7"/>
       <c r="C137" s="2"/>
     </row>
     <row r="138" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="3"/>
-      <c r="B138" s="2"/>
+      <c r="B138" s="7"/>
       <c r="C138" s="2"/>
     </row>
     <row r="139" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="3"/>
-      <c r="B139" s="2"/>
+      <c r="B139" s="7"/>
       <c r="C139" s="2"/>
     </row>
     <row r="140" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="3"/>
-      <c r="B140" s="2"/>
+      <c r="B140" s="7"/>
       <c r="C140" s="2"/>
     </row>
     <row r="141" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="3"/>
-      <c r="B141" s="2"/>
+      <c r="B141" s="7"/>
       <c r="C141" s="2"/>
     </row>
     <row r="142" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="3"/>
-      <c r="B142" s="2"/>
+      <c r="B142" s="7"/>
       <c r="C142" s="2"/>
     </row>
     <row r="143" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="3"/>
-      <c r="B143" s="2"/>
+      <c r="B143" s="7"/>
       <c r="C143" s="2"/>
     </row>
     <row r="144" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="3"/>
-      <c r="B144" s="2"/>
+      <c r="B144" s="7"/>
       <c r="C144" s="2"/>
     </row>
     <row r="145" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="3"/>
-      <c r="B145" s="2"/>
+      <c r="B145" s="7"/>
       <c r="C145" s="2"/>
     </row>
     <row r="146" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="3"/>
-      <c r="B146" s="2"/>
+      <c r="B146" s="7"/>
       <c r="C146" s="2"/>
     </row>
     <row r="147" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="3"/>
-      <c r="B147" s="2"/>
+      <c r="B147" s="7"/>
       <c r="C147" s="2"/>
     </row>
     <row r="148" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="3"/>
-      <c r="B148" s="2"/>
+      <c r="B148" s="7"/>
       <c r="C148" s="2"/>
     </row>
     <row r="149" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="3"/>
-      <c r="B149" s="2"/>
+      <c r="B149" s="7"/>
       <c r="C149" s="2"/>
     </row>
     <row r="150" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="3"/>
-      <c r="B150" s="2"/>
+      <c r="B150" s="7"/>
       <c r="C150" s="2"/>
     </row>
     <row r="151" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="3"/>
-      <c r="B151" s="2"/>
+      <c r="B151" s="7"/>
       <c r="C151" s="2"/>
     </row>
     <row r="152" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="3"/>
-      <c r="B152" s="2"/>
+      <c r="B152" s="7"/>
       <c r="C152" s="2"/>
     </row>
     <row r="153" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="3"/>
-      <c r="B153" s="2"/>
+      <c r="B153" s="7"/>
       <c r="C153" s="2"/>
     </row>
     <row r="154" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="3"/>
-      <c r="B154" s="2"/>
+      <c r="B154" s="7"/>
       <c r="C154" s="2"/>
     </row>
     <row r="155" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="3"/>
-      <c r="B155" s="2"/>
+      <c r="B155" s="7"/>
       <c r="C155" s="2"/>
     </row>
     <row r="156" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="3"/>
-      <c r="B156" s="2"/>
+      <c r="B156" s="7"/>
       <c r="C156" s="2"/>
     </row>
     <row r="157" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="3"/>
-      <c r="B157" s="2"/>
+      <c r="B157" s="7"/>
       <c r="C157" s="2"/>
     </row>
     <row r="158" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="3"/>
-      <c r="B158" s="2"/>
+      <c r="B158" s="7"/>
       <c r="C158" s="2"/>
     </row>
     <row r="159" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="3"/>
-      <c r="B159" s="2"/>
+      <c r="B159" s="7"/>
       <c r="C159" s="2"/>
     </row>
     <row r="160" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="3"/>
-      <c r="B160" s="2"/>
+      <c r="B160" s="7"/>
       <c r="C160" s="2"/>
     </row>
     <row r="161" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="3"/>
-      <c r="B161" s="2"/>
+      <c r="B161" s="7"/>
       <c r="C161" s="2"/>
     </row>
     <row r="162" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="3"/>
-      <c r="B162" s="2"/>
+      <c r="B162" s="7"/>
       <c r="C162" s="2"/>
     </row>
     <row r="163" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="3"/>
-      <c r="B163" s="2"/>
+      <c r="B163" s="7"/>
       <c r="C163" s="2"/>
     </row>
     <row r="164" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="3"/>
-      <c r="B164" s="2"/>
+      <c r="B164" s="7"/>
       <c r="C164" s="2"/>
     </row>
     <row r="165" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="3"/>
-      <c r="B165" s="2"/>
+      <c r="B165" s="7"/>
       <c r="C165" s="2"/>
     </row>
     <row r="166" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="3"/>
-      <c r="B166" s="2"/>
+      <c r="B166" s="7"/>
       <c r="C166" s="2"/>
     </row>
     <row r="167" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="3"/>
-      <c r="B167" s="2"/>
+      <c r="B167" s="7"/>
       <c r="C167" s="2"/>
     </row>
     <row r="168" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="3"/>
-      <c r="B168" s="2"/>
+      <c r="B168" s="7"/>
       <c r="C168" s="2"/>
     </row>
     <row r="169" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="3"/>
-      <c r="B169" s="2"/>
+      <c r="B169" s="7"/>
       <c r="C169" s="2"/>
     </row>
     <row r="170" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="3"/>
-      <c r="B170" s="2"/>
+      <c r="B170" s="7"/>
       <c r="C170" s="2"/>
     </row>
     <row r="171" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="3"/>
-      <c r="B171" s="2"/>
+      <c r="B171" s="7"/>
       <c r="C171" s="2"/>
     </row>
     <row r="172" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="3"/>
-      <c r="B172" s="2"/>
+      <c r="B172" s="7"/>
       <c r="C172" s="2"/>
     </row>
     <row r="173" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="3"/>
-      <c r="B173" s="2"/>
+      <c r="B173" s="7"/>
       <c r="C173" s="2"/>
     </row>
     <row r="174" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="3"/>
-      <c r="B174" s="2"/>
+      <c r="B174" s="7"/>
       <c r="C174" s="2"/>
     </row>
     <row r="175" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="3"/>
-      <c r="B175" s="2"/>
+      <c r="B175" s="7"/>
       <c r="C175" s="2"/>
     </row>
     <row r="176" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="3"/>
-      <c r="B176" s="2"/>
+      <c r="B176" s="7"/>
       <c r="C176" s="2"/>
     </row>
     <row r="177" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="3"/>
-      <c r="B177" s="2"/>
+      <c r="B177" s="7"/>
       <c r="C177" s="2"/>
     </row>
     <row r="178" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="3"/>
-      <c r="B178" s="2"/>
+      <c r="B178" s="7"/>
       <c r="C178" s="2"/>
     </row>
     <row r="179" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="3"/>
-      <c r="B179" s="2"/>
+      <c r="B179" s="7"/>
       <c r="C179" s="2"/>
     </row>
     <row r="180" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="3"/>
-      <c r="B180" s="2"/>
+      <c r="B180" s="7"/>
       <c r="C180" s="2"/>
     </row>
     <row r="181" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="3"/>
-      <c r="B181" s="2"/>
+      <c r="B181" s="7"/>
       <c r="C181" s="2"/>
     </row>
     <row r="182" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="3"/>
-      <c r="B182" s="2"/>
+      <c r="B182" s="7"/>
       <c r="C182" s="2"/>
     </row>
     <row r="183" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="3"/>
-      <c r="B183" s="2"/>
+      <c r="B183" s="7"/>
       <c r="C183" s="2"/>
     </row>
     <row r="184" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="3"/>
-      <c r="B184" s="2"/>
+      <c r="B184" s="7"/>
       <c r="C184" s="2"/>
     </row>
     <row r="185" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="3"/>
-      <c r="B185" s="2"/>
+      <c r="B185" s="7"/>
       <c r="C185" s="2"/>
     </row>
     <row r="186" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="3"/>
-      <c r="B186" s="2"/>
+      <c r="B186" s="7"/>
       <c r="C186" s="2"/>
     </row>
     <row r="187" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="3"/>
-      <c r="B187" s="2"/>
+      <c r="B187" s="7"/>
       <c r="C187" s="2"/>
     </row>
     <row r="188" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="3"/>
-      <c r="B188" s="2"/>
+      <c r="B188" s="7"/>
       <c r="C188" s="2"/>
     </row>
     <row r="189" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="3"/>
-      <c r="B189" s="2"/>
+      <c r="B189" s="7"/>
       <c r="C189" s="2"/>
     </row>
     <row r="190" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="3"/>
-      <c r="B190" s="2"/>
+      <c r="B190" s="7"/>
       <c r="C190" s="2"/>
     </row>
     <row r="191" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="3"/>
-      <c r="B191" s="2"/>
+      <c r="B191" s="7"/>
       <c r="C191" s="2"/>
     </row>
     <row r="192" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="3"/>
-      <c r="B192" s="2"/>
+      <c r="B192" s="7"/>
       <c r="C192" s="2"/>
     </row>
     <row r="193" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="3"/>
-      <c r="B193" s="2"/>
+      <c r="B193" s="7"/>
       <c r="C193" s="2"/>
     </row>
     <row r="194" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="3"/>
-      <c r="B194" s="2"/>
+      <c r="B194" s="7"/>
       <c r="C194" s="2"/>
     </row>
     <row r="195" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="3"/>
-      <c r="B195" s="2"/>
+      <c r="B195" s="7"/>
       <c r="C195" s="2"/>
     </row>
     <row r="196" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="3"/>
-      <c r="B196" s="2"/>
+      <c r="B196" s="7"/>
       <c r="C196" s="2"/>
     </row>
     <row r="197" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="3"/>
-      <c r="B197" s="2"/>
+      <c r="B197" s="7"/>
       <c r="C197" s="2"/>
     </row>
     <row r="198" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="3"/>
-      <c r="B198" s="2"/>
+      <c r="B198" s="7"/>
       <c r="C198" s="2"/>
     </row>
     <row r="199" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="3"/>
-      <c r="B199" s="2"/>
+      <c r="B199" s="7"/>
       <c r="C199" s="2"/>
     </row>
     <row r="200" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="3"/>
-      <c r="B200" s="2"/>
+      <c r="B200" s="7"/>
       <c r="C200" s="2"/>
     </row>
     <row r="201" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="3"/>
-      <c r="B201" s="2"/>
+      <c r="B201" s="7"/>
       <c r="C201" s="2"/>
     </row>
     <row r="202" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="3"/>
-      <c r="B202" s="2"/>
+      <c r="B202" s="7"/>
       <c r="C202" s="2"/>
     </row>
     <row r="203" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="3"/>
-      <c r="B203" s="2"/>
+      <c r="B203" s="7"/>
       <c r="C203" s="2"/>
     </row>
     <row r="204" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="3"/>
-      <c r="B204" s="2"/>
+      <c r="B204" s="7"/>
       <c r="C204" s="2"/>
     </row>
     <row r="205" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="3"/>
-      <c r="B205" s="2"/>
+      <c r="B205" s="7"/>
       <c r="C205" s="2"/>
     </row>
     <row r="206" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="3"/>
-      <c r="B206" s="2"/>
+      <c r="B206" s="7"/>
       <c r="C206" s="2"/>
     </row>
     <row r="207" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" s="3"/>
-      <c r="B207" s="2"/>
+      <c r="B207" s="7"/>
       <c r="C207" s="2"/>
     </row>
     <row r="208" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="3"/>
-      <c r="B208" s="2"/>
+      <c r="B208" s="7"/>
       <c r="C208" s="2"/>
     </row>
     <row r="209" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="3"/>
-      <c r="B209" s="2"/>
+      <c r="B209" s="7"/>
       <c r="C209" s="2"/>
     </row>
     <row r="210" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" s="3"/>
-      <c r="B210" s="2"/>
+      <c r="B210" s="7"/>
       <c r="C210" s="2"/>
     </row>
     <row r="211" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="3"/>
-      <c r="B211" s="2"/>
+      <c r="B211" s="7"/>
       <c r="C211" s="2"/>
     </row>
     <row r="212" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="3"/>
-      <c r="B212" s="2"/>
+      <c r="B212" s="7"/>
       <c r="C212" s="2"/>
     </row>
     <row r="213" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="3"/>
-      <c r="B213" s="2"/>
+      <c r="B213" s="7"/>
       <c r="C213" s="2"/>
     </row>
     <row r="214" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="3"/>
-      <c r="B214" s="2"/>
+      <c r="B214" s="7"/>
       <c r="C214" s="2"/>
     </row>
     <row r="215" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="3"/>
-      <c r="B215" s="2"/>
+      <c r="B215" s="7"/>
       <c r="C215" s="2"/>
     </row>
     <row r="216" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" s="3"/>
-      <c r="B216" s="2"/>
+      <c r="B216" s="7"/>
       <c r="C216" s="2"/>
     </row>
     <row r="217" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" s="3"/>
-      <c r="B217" s="2"/>
+      <c r="B217" s="7"/>
       <c r="C217" s="2"/>
     </row>
     <row r="218" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" s="3"/>
-      <c r="B218" s="2"/>
+      <c r="B218" s="7"/>
       <c r="C218" s="2"/>
     </row>
     <row r="219" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" s="3"/>
-      <c r="B219" s="2"/>
+      <c r="B219" s="7"/>
       <c r="C219" s="2"/>
     </row>
     <row r="220" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="3"/>
-      <c r="B220" s="2"/>
+      <c r="B220" s="7"/>
       <c r="C220" s="2"/>
     </row>
     <row r="221" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" s="3"/>
-      <c r="B221" s="2"/>
+      <c r="B221" s="7"/>
       <c r="C221" s="2"/>
     </row>
     <row r="222" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" s="3"/>
-      <c r="B222" s="2"/>
+      <c r="B222" s="7"/>
       <c r="C222" s="2"/>
     </row>
     <row r="223" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" s="3"/>
-      <c r="B223" s="2"/>
+      <c r="B223" s="7"/>
       <c r="C223" s="2"/>
     </row>
     <row r="224" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" s="3"/>
-      <c r="B224" s="2"/>
+      <c r="B224" s="7"/>
       <c r="C224" s="2"/>
     </row>
     <row r="225" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="3"/>
-      <c r="B225" s="2"/>
+      <c r="B225" s="7"/>
       <c r="C225" s="2"/>
     </row>
     <row r="226" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" s="3"/>
-      <c r="B226" s="2"/>
+      <c r="B226" s="7"/>
       <c r="C226" s="2"/>
     </row>
     <row r="227" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" s="3"/>
-      <c r="B227" s="2"/>
+      <c r="B227" s="7"/>
       <c r="C227" s="2"/>
     </row>
     <row r="228" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" s="3"/>
-      <c r="B228" s="2"/>
+      <c r="B228" s="7"/>
       <c r="C228" s="2"/>
     </row>
     <row r="229" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229" s="3"/>
-      <c r="B229" s="2"/>
+      <c r="B229" s="7"/>
       <c r="C229" s="2"/>
     </row>
     <row r="230" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" s="3"/>
-      <c r="B230" s="2"/>
+      <c r="B230" s="7"/>
       <c r="C230" s="2"/>
     </row>
     <row r="231" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231" s="3"/>
-      <c r="B231" s="2"/>
+      <c r="B231" s="7"/>
       <c r="C231" s="2"/>
     </row>
     <row r="232" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" s="3"/>
-      <c r="B232" s="2"/>
+      <c r="B232" s="7"/>
       <c r="C232" s="2"/>
     </row>
     <row r="233" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" s="3"/>
-      <c r="B233" s="2"/>
+      <c r="B233" s="7"/>
       <c r="C233" s="2"/>
     </row>
     <row r="234" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" s="3"/>
-      <c r="B234" s="2"/>
+      <c r="B234" s="7"/>
       <c r="C234" s="2"/>
     </row>
     <row r="235" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -2279,6 +2402,6 @@
     <row r="983" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup orientation="landscape"/>
+  <pageSetup orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>